--- a/data/trans_camb/IP21-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -0,25</t>
+          <t>-14,17; -0,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -4,92</t>
+          <t>-18,18; -5,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -8,39</t>
+          <t>-21,07; -8,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,69; -0,6</t>
+          <t>-11,96; 0,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -3,41</t>
+          <t>-14,62; -2,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -3,2</t>
+          <t>-15,55; -2,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -1,93</t>
+          <t>-11,58; -1,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -5,99</t>
+          <t>-14,57; -5,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -6,92</t>
+          <t>-16,02; -7,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 0,53</t>
+          <t>-68,01; -2,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,56; -35,59</t>
+          <t>-86,34; -41,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,87; -57,82</t>
+          <t>-96,69; -55,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,61; -1,43</t>
+          <t>-70,77; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,1; -26,8</t>
+          <t>-83,31; -25,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,56; -20,22</t>
+          <t>-89,66; -18,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,81; -15,57</t>
+          <t>-62,23; -14,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,76; -45,19</t>
+          <t>-79,79; -43,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,39; -49,59</t>
+          <t>-91,29; -54,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,98</t>
+          <t>0,88; 5,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,49</t>
+          <t>-0,49; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,22</t>
+          <t>-0,69; 4,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,24</t>
+          <t>-1,75; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,55</t>
+          <t>-4,67; -0,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,31</t>
+          <t>-4,54; 0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,52</t>
+          <t>0,43; 4,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,11</t>
+          <t>-1,91; 1,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,4</t>
+          <t>-1,97; 1,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 837,57</t>
+          <t>19,57; 703,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 721,36</t>
+          <t>-32,86; 537,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 506,65</t>
+          <t>-42,63; 567,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 171,59</t>
+          <t>-38,33; 171,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,72; -5,18</t>
+          <t>-91,29; -2,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 28,46</t>
+          <t>-83,26; 40,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 247,98</t>
+          <t>10,51; 219,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 70,36</t>
+          <t>-57,93; 60,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,76; 77,95</t>
+          <t>-58,56; 73,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,16</t>
+          <t>-3,36; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,07</t>
+          <t>-2,09; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,65</t>
+          <t>-2,75; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,28</t>
+          <t>-4,33; 2,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,54</t>
+          <t>-3,69; 2,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,45</t>
+          <t>-5,33; 0,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,99</t>
+          <t>-2,78; 1,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,99</t>
+          <t>-2,06; 1,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,49</t>
+          <t>-3,01; 0,52</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,71; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,87; 163,57</t>
+          <t>-82,62; 179,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 167,76</t>
+          <t>-75,94; 187,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,54</t>
+          <t>-100,0; 99,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 98,68</t>
+          <t>-78,35; 92,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 143,16</t>
+          <t>-57,12; 133,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 73,29</t>
+          <t>-84,11; 59,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,08</t>
+          <t>-1,34; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,34</t>
+          <t>-0,72; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,38</t>
+          <t>-2,03; 0,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,3</t>
+          <t>-0,67; 4,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,33</t>
+          <t>0,01; 5,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,86</t>
+          <t>-1,72; 1,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,58</t>
+          <t>-0,46; 2,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,52</t>
+          <t>0,03; 3,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,92</t>
+          <t>-1,4; 0,87</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>-63,37; —</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,25; 919,73</t>
+          <t>-50,68; 902,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 1232,92</t>
+          <t>-28,43; 1165,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,08; 529,71</t>
+          <t>-86,8; inf</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 427,68</t>
+          <t>-35,66; 457,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 557,58</t>
+          <t>-15,65; 600,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,27; 212,94</t>
+          <t>-82,16; 154,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,96</t>
+          <t>-1,25; 1,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,88</t>
+          <t>-2,23; 0,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,88</t>
+          <t>-3,7; -1,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,54</t>
+          <t>-1,91; 1,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,14</t>
+          <t>-3,28; -0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,33</t>
+          <t>-4,57; -1,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,27</t>
+          <t>-1,11; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,24</t>
+          <t>-2,38; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,7</t>
+          <t>-3,7; -1,71</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 65,78</t>
+          <t>-28,2; 61,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 30,64</t>
+          <t>-49,63; 29,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,35; -29,27</t>
+          <t>-81,08; -35,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 42,21</t>
+          <t>-35,07; 40,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-61,94; -2,67</t>
+          <t>-60,88; -4,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -36,7</t>
+          <t>-80,48; -38,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 35,77</t>
+          <t>-23,71; 35,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,87; -5,46</t>
+          <t>-49,0; -3,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -46,52</t>
+          <t>-77,64; -46,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -0,15</t>
+          <t>-14,12; -0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -5,27</t>
+          <t>-18,27; -5,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -8,43</t>
+          <t>-20,84; -8,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 0,07</t>
+          <t>-12,69; 0,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -2,82</t>
+          <t>-14,51; -3,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -2,63</t>
+          <t>-14,99; -2,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -1,92</t>
+          <t>-11,16; -1,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -5,77</t>
+          <t>-15,09; -5,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -7,45</t>
+          <t>-16,14; -7,3</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,01; -2,43</t>
+          <t>-68,0; -1,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,34; -41,28</t>
+          <t>-85,3; -35,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,69; -55,26</t>
+          <t>-96,9; -52,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 4,39</t>
+          <t>-72,81; 4,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,31; -25,19</t>
+          <t>-85,07; -28,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,66; -18,06</t>
+          <t>-88,65; -12,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,23; -14,1</t>
+          <t>-62,38; -13,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -43,59</t>
+          <t>-80,69; -43,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,29; -54,31</t>
+          <t>-90,01; -53,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,87</t>
+          <t>1,0; 6,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,08</t>
+          <t>-0,29; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,27</t>
+          <t>-0,64; 4,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,2</t>
+          <t>-1,48; 4,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,45</t>
+          <t>-4,54; -0,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,37</t>
+          <t>-4,23; 0,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,15</t>
+          <t>0,3; 4,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,1</t>
+          <t>-1,99; 1,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,46</t>
+          <t>-1,94; 1,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,57; 703,97</t>
+          <t>21,48; 917,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 537,45</t>
+          <t>-22,58; 559,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 567,38</t>
+          <t>-46,22; 592,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 171,13</t>
+          <t>-33,12; 195,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,29; -2,63</t>
+          <t>-88,3; 0,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 40,73</t>
+          <t>-83,14; 39,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 219,77</t>
+          <t>5,18; 241,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,93; 60,83</t>
+          <t>-59,11; 71,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 73,62</t>
+          <t>-58,89; 79,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,95</t>
+          <t>-3,15; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,74</t>
+          <t>-1,67; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,69</t>
+          <t>-2,9; 1,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,54</t>
+          <t>-3,82; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,46</t>
+          <t>-3,89; 2,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,47</t>
+          <t>-5,24; 0,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,07</t>
+          <t>-2,73; 1,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,86</t>
+          <t>-1,94; 2,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,52</t>
+          <t>-3,08; 0,47</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-74,64; 932,89</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,62; 179,48</t>
+          <t>-83,79; 170,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 187,73</t>
+          <t>-76,1; 173,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 99,53</t>
+          <t>-100,0; 92,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 92,54</t>
+          <t>-76,76; 106,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 133,38</t>
+          <t>-56,6; 156,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 59,53</t>
+          <t>-84,17; 46,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,03</t>
+          <t>-1,21; 2,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,27</t>
+          <t>-0,72; 3,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,51</t>
+          <t>-2,02; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,26</t>
+          <t>-0,61; 4,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,42</t>
+          <t>-0,06; 5,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,86</t>
+          <t>-1,88; 1,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,62</t>
+          <t>-0,4; 2,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,64</t>
+          <t>0,17; 3,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,87</t>
+          <t>-1,46; 0,76</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,37; —</t>
+          <t>-65,86; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 902,36</t>
+          <t>-44,61; 836,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 1165,63</t>
+          <t>-36,19; 1121,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,8; inf</t>
+          <t>-91,21; 390,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 457,37</t>
+          <t>-35,99; 407,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 600,19</t>
+          <t>-7,28; 531,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 154,57</t>
+          <t>-80,89; 178,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,83</t>
+          <t>-1,43; 1,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,84</t>
+          <t>-2,18; 0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,07</t>
+          <t>-3,79; -1,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,52</t>
+          <t>-1,94; 1,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,2</t>
+          <t>-3,37; -0,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -1,6</t>
+          <t>-4,47; -1,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,21</t>
+          <t>-1,22; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,17</t>
+          <t>-2,34; -0,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,71</t>
+          <t>-3,71; -1,72</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 61,66</t>
+          <t>-30,8; 66,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 29,61</t>
+          <t>-49,13; 25,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -35,09</t>
+          <t>-79,88; -31,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 40,78</t>
+          <t>-35,0; 45,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,88; -4,17</t>
+          <t>-61,92; -3,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,48; -38,28</t>
+          <t>-79,56; -32,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 35,79</t>
+          <t>-25,63; 35,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -3,91</t>
+          <t>-49,36; -4,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,64; -46,27</t>
+          <t>-76,34; -46,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-6,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,81</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,54</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-11,44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-14,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,81</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,09</t>
+          <t>-14,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-11,53</t>
+          <t>-11,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -0,21</t>
+          <t>-12,69; -0,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -5,25</t>
+          <t>-15,05; -3,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -8,17</t>
+          <t>-14,82; -2,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 0,21</t>
+          <t>-13,9; -0,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -3,0</t>
+          <t>-18,08; -4,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,99; -2,26</t>
+          <t>-20,74; -8,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -1,94</t>
+          <t>-10,92; -1,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,09; -5,84</t>
+          <t>-14,52; -5,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -7,3</t>
+          <t>-15,73; -6,65</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-65,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-63,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-41,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-68,76%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-85,65%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-65,34%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-67,41%</t>
+          <t>-86,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-77,08%</t>
+          <t>-75,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,0; -1,83</t>
+          <t>-73,61; -1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,3; -35,05</t>
+          <t>-86,1; -26,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-96,9; -52,52</t>
+          <t>-88,49; -9,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,81; 4,87</t>
+          <t>-65,01; 0,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,07; -28,12</t>
+          <t>-85,56; -35,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,65; -12,42</t>
+          <t>-97,35; -58,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -13,69</t>
+          <t>-61,81; -15,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,69; -43,95</t>
+          <t>-80,76; -45,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,01; -53,71</t>
+          <t>-89,08; -47,81</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,08</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,14</t>
+          <t>-1,91; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,44</t>
+          <t>-4,91; -0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,37</t>
+          <t>-4,29; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,48</t>
+          <t>0,8; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,22</t>
+          <t>-0,19; 4,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,48</t>
+          <t>-0,83; 4,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,3</t>
+          <t>0,44; 4,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,18</t>
+          <t>-2,03; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,4</t>
+          <t>-1,93; 1,53</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-65,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-56,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>200,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>116,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-65,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-52,25%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,32%</t>
+          <t>-12,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 917,3</t>
+          <t>-39,11; 171,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 559,54</t>
+          <t>-91,72; -5,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 592,13</t>
+          <t>-85,64; 19,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 195,1</t>
+          <t>14,86; 837,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 0,33</t>
+          <t>-17,23; 721,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,14; 39,37</t>
+          <t>-55,39; 543,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 241,75</t>
+          <t>8,87; 247,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 71,81</t>
+          <t>-58,63; 70,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,89; 79,85</t>
+          <t>-60,3; 82,1</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,62</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,2</t>
+          <t>-4,13; 2,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,21</t>
+          <t>-3,85; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,5</t>
+          <t>-5,7; 0,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,27</t>
+          <t>-3,24; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 2,31</t>
+          <t>-1,81; 3,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,55</t>
+          <t>-3,18; 1,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,05</t>
+          <t>-2,92; 0,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,14</t>
+          <t>-1,89; 1,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,47</t>
+          <t>-3,19; 0,39</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-26,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-15,88%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-63,33%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-44,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>40,2%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-22,56%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-26,3%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-15,88%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-60,72%</t>
+          <t>-25,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-49,39%</t>
+          <t>-52,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-86,87; 163,57</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-76,58; 167,76</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 70,09</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-74,64; 932,89</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-83,79; 170,18</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 173,68</t>
+          <t>-71,71; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,01</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,76; 106,27</t>
+          <t>-81,0; 98,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 156,97</t>
+          <t>-55,66; 143,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,17; 46,59</t>
+          <t>-86,55; 58,86</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,96</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,32</t>
+          <t>-0,65; 4,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,44</t>
+          <t>-0,05; 5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,47</t>
+          <t>-1,69; 2,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,13</t>
+          <t>-1,29; 2,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,45</t>
+          <t>-0,91; 3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,76</t>
+          <t>-2,28; 0,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,53</t>
+          <t>-0,44; 2,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,42</t>
+          <t>0,1; 3,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,76</t>
+          <t>-1,29; 1,06</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>125,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>174,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-0,69%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>20,94%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-53,01%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>125,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>174,76%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,92%</t>
+          <t>-50,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,0%</t>
+          <t>-19,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-47,25; 919,73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-23,37; 1232,92</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-86,55; 620,12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-65,86; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-44,61; 836,93</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-36,19; 1121,61</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,21; 390,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 407,44</t>
+          <t>-34,03; 427,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 531,8</t>
+          <t>-4,64; 557,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,89; 178,84</t>
+          <t>-77,44; 233,74</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,97</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,95</t>
+          <t>-1,92; 1,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,8</t>
+          <t>-3,52; -0,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -1,04</t>
+          <t>-4,53; -1,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,64</t>
+          <t>-1,41; 1,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,13</t>
+          <t>-2,23; 0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -1,39</t>
+          <t>-3,69; -0,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,28</t>
+          <t>-1,34; 1,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,14</t>
+          <t>-2,42; -0,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -1,72</t>
+          <t>-3,7; -1,69</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-3,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-39,43%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-64,78%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-62,86%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-3,43%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-39,43%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-64,35%</t>
+          <t>-62,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-63,59%</t>
+          <t>-63,65%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 66,89</t>
+          <t>-34,68; 42,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 25,8</t>
+          <t>-61,94; -2,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-79,88; -31,95</t>
+          <t>-80,71; -36,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 45,41</t>
+          <t>-31,31; 65,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -3,66</t>
+          <t>-48,44; 30,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,56; -32,97</t>
+          <t>-80,36; -29,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 35,94</t>
+          <t>-28,09; 35,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -4,05</t>
+          <t>-49,87; -5,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -46,09</t>
+          <t>-76,49; -46,32</t>
         </is>
       </c>
     </row>
